--- a/membership_forms/025_urban_planners_guild_membership_form--membership_forms.xlsx
+++ b/membership_forms/025_urban_planners_guild_membership_form--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Member Details</t>
+          <t>Member Details Repeat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Member Type</t>
+          <t>Member Type Options</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Organization Repeat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address Repeat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Experience Years</t>
+          <t>Experience Years Repeat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note Repeat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Cancel Repeat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Member Details</t>
+          <t>Member Details Repeat 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Experience Years</t>
+          <t>Experience Years Repeat 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note Repeat 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Organization Repeat 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,274 +1199,274 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>member_details_repeat_choices</t>
+          <t>member_type_options_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>member_details_repeat_choices</t>
+          <t>member_type_options_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>non-member</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Non-Member</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>member_details_repeat_choices</t>
+          <t>member_type_repeat_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>member_details_repeat_choices</t>
+          <t>member_type_repeat_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>member_details_repeat_choices</t>
+          <t>member_type_repeat_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>member_details_repeat_choices</t>
+          <t>organization_repeat_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>member_type_options_choices</t>
+          <t>organization_repeat_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>member_type_options_choices</t>
+          <t>address_repeat_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>non-member</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Non-Member</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>member_type_repeat_choices</t>
+          <t>address_repeat_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>member_type_repeat_choices</t>
+          <t>experience_years_repeat_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>organization_repeat_choices</t>
+          <t>experience_years_repeat_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>organization_repeat_choices</t>
+          <t>note_repeat_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>address_repeat_choices</t>
+          <t>note_repeat_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>address_repeat_choices</t>
+          <t>member_details_repeat_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>experience_years_repeat_choices</t>
+          <t>member_details_repeat_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>experience_years_repeat_choices</t>
+          <t>member_details_repeat_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,24 +1483,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>note_repeat_choices</t>
+          <t>experience_years_repeat_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note_repeat_choices</t>
+          <t>experience_years_repeat_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,58 +1517,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>member_details_repeat_2_choices</t>
+          <t>note_repeat_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>member_details_repeat_2_choices</t>
+          <t>note_repeat_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>experience_years_repeat_2_choices</t>
+          <t>organization_repeat_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>experience_years_repeat_2_choices</t>
+          <t>organization_repeat_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1577,74 +1577,6 @@
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>note_repeat_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>note_repeat_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>organization_repeat_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>organization_repeat_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
